--- a/CALCCCS - 13-07-2026 MEDI2101B Timetable - CANVAS-1.xlsx
+++ b/CALCCCS - 13-07-2026 MEDI2101B Timetable - CANVAS-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uonstaff.sharepoint.com/sites/smph/MDCurriculum/Documents  Phase 1 Only/Timetables, Groups, Attendance Templates/2026/Year 2/S2/Timetable/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sudesh/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0E949F27-62DE-4332-BDC9-676C328BEB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{808D39A7-73AE-42F8-ABBB-995E1263CFAB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BD3068-CEAD-8141-87AF-BE2C1A23E906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C83A5B6-A249-407B-83A1-4DACB0EAB497}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="56300" windowHeight="31040" xr2:uid="{0C83A5B6-A249-407B-83A1-4DACB0EAB497}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="102">
   <si>
     <t>Scheduled Weeks</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Wed</t>
-  </si>
-  <si>
-    <t>9:00am -10:00am</t>
   </si>
   <si>
     <t>CAL/CC</t>
@@ -357,7 +354,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -708,28 +705,28 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1066,24 +1063,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4022729E-D7BB-48C2-ACBB-42A593A3F5BE}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,7 +1121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1134,1095 +1131,1095 @@
       <c r="C2" s="48">
         <v>46218</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
+      <c r="D2" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="49">
         <v>46219</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="H3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="50">
         <v>46219</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="14">
         <v>1.5</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="I4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="50">
         <v>46219</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="14">
         <v>1.5</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="50">
         <v>46219</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="19">
         <v>1.5</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="H6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="I6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="50">
         <v>46219</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="19">
         <v>1.5</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H7" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="51">
         <v>46219</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="22">
         <v>2</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="I8" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="51">
         <v>46219</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="30">
         <v>2</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="I9" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="51">
         <v>46219</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="32">
         <v>2</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="I10" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10" s="33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="51">
         <v>46219</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="32">
         <v>2</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="I11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="51">
         <v>46219</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="32">
         <v>2</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="I12" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="51">
         <v>46219</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="32">
         <v>2</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="I13" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="51">
         <v>46219</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="32">
         <v>2</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="35" t="s">
+      <c r="I14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="51">
         <v>46219</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="32">
         <v>2</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="I15" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="51">
         <v>46219</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="32">
         <v>2</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="I16" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I16" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="51">
         <v>46219</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="32">
         <v>2</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="I17" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M17" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="51">
         <v>46219</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="32">
         <v>2</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H18" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18" s="28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="51">
         <v>46219</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" s="32">
         <v>2</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="51">
         <v>46219</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="32">
         <v>2</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="51">
         <v>46219</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" s="32">
         <v>2</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L21" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M21" s="28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="51">
         <v>46219</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="32">
         <v>2</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M22" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="H22" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M22" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="51">
         <v>46219</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" s="32">
         <v>2</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M23" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="51">
         <v>46219</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="32">
         <v>2</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H24" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K24" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M24" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="51">
         <v>46219</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="32">
         <v>2</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H25" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="L25" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M25" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="52">
         <v>46219</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="32">
         <v>2</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J26" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="39" t="s">
+      <c r="L26" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="L26" s="40" t="s">
-        <v>52</v>
-      </c>
       <c r="M26" s="38" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" s="53">
         <v>46220</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="42">
         <v>1.5</v>
       </c>
       <c r="F27" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="H27" s="43" t="s">
         <v>17</v>
-      </c>
-      <c r="H27" s="43" t="s">
-        <v>18</v>
       </c>
       <c r="I27" s="41"/>
       <c r="J27" s="41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K27" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="L27" s="45" t="s">
-        <v>98</v>
-      </c>
       <c r="M27" s="44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="53">
         <v>46220</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="42">
         <v>1</v>
       </c>
       <c r="F28" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="41" t="s">
-        <v>17</v>
-      </c>
       <c r="H28" s="46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28" s="41"/>
       <c r="J28" s="41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="L28" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="L28" s="45" t="s">
-        <v>102</v>
-      </c>
       <c r="M28" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2231,10 +2228,20 @@
     <hyperlink ref="H27" r:id="rId2" xr:uid="{E7A8AEAA-B953-49AF-B8B6-695CE41AE6BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <MD_x0020_Owner xmlns="dc764086-fd63-4649-bef6-f0cf9e9c3d37">
@@ -2256,15 +2263,6 @@
     <MD_x0020_Category xmlns="dc764086-fd63-4649-bef6-f0cf9e9c3d37" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2603,6 +2601,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC71D0D9-4423-45B4-B1B6-5C21E03BF088}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B793B38E-86AD-4726-BC9A-6B3895D71C59}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2610,14 +2616,6 @@
     <ds:schemaRef ds:uri="dc764086-fd63-4649-bef6-f0cf9e9c3d37"/>
     <ds:schemaRef ds:uri="cfbb25e3-15ec-4c4e-acd4-82a69ff8e131"/>
     <ds:schemaRef ds:uri="ae5394b7-e16c-4952-833f-5730ecb68a4d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC71D0D9-4423-45B4-B1B6-5C21E03BF088}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
